--- a/final_data_pipeline/output/325194longform.xlsx
+++ b/final_data_pipeline/output/325194longform.xlsx
@@ -870,7 +870,7 @@
         <v>101</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -959,7 +959,7 @@
         <v>101</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -1048,7 +1048,7 @@
         <v>101</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1137,7 +1137,7 @@
         <v>101</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1226,7 +1226,7 @@
         <v>101</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1315,7 +1315,7 @@
         <v>101</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1404,7 +1404,7 @@
         <v>101</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1493,7 +1493,7 @@
         <v>101</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1582,7 +1582,7 @@
         <v>101</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1671,7 +1671,7 @@
         <v>101</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1760,7 +1760,7 @@
         <v>101</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -1849,7 +1849,7 @@
         <v>101</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -1938,7 +1938,7 @@
         <v>101</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -2027,7 +2027,7 @@
         <v>101</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -2116,7 +2116,7 @@
         <v>101</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -2205,7 +2205,7 @@
         <v>101</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB17">
         <v>8000</v>
@@ -2294,7 +2294,7 @@
         <v>101</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB18">
         <v>8000</v>
@@ -2383,7 +2383,7 @@
         <v>102</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB19">
         <v>8000</v>
@@ -2472,7 +2472,7 @@
         <v>102</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2561,7 +2561,7 @@
         <v>102</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -2650,7 +2650,7 @@
         <v>102</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB22">
         <v>8000</v>
@@ -2739,7 +2739,7 @@
         <v>102</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB23">
         <v>8000</v>
@@ -2828,7 +2828,7 @@
         <v>102</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB24">
         <v>8000</v>
@@ -2917,7 +2917,7 @@
         <v>101</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB25">
         <v>8000</v>
@@ -4789,7 +4789,7 @@
         <v>102</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB46">
         <v>8000</v>
@@ -4881,7 +4881,7 @@
         <v>102</v>
       </c>
       <c r="AA47">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB47">
         <v>8000</v>
@@ -4973,7 +4973,7 @@
         <v>102</v>
       </c>
       <c r="AA48">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB48">
         <v>8000</v>
@@ -5062,7 +5062,7 @@
         <v>101</v>
       </c>
       <c r="AA49">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB49">
         <v>8000</v>
@@ -5151,7 +5151,7 @@
         <v>102</v>
       </c>
       <c r="AA50">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB50">
         <v>8000</v>
@@ -5240,7 +5240,7 @@
         <v>101</v>
       </c>
       <c r="AA51">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB51">
         <v>8000</v>
@@ -5329,7 +5329,7 @@
         <v>101</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5418,7 +5418,7 @@
         <v>101</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5507,7 +5507,7 @@
         <v>101</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5596,7 +5596,7 @@
         <v>101</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -5685,7 +5685,7 @@
         <v>102</v>
       </c>
       <c r="AA56">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AB56">
         <v>8000</v>
@@ -7198,7 +7198,7 @@
         <v>101</v>
       </c>
       <c r="AA73">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB73">
         <v>8000</v>
@@ -7287,7 +7287,7 @@
         <v>101</v>
       </c>
       <c r="AA74">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB74">
         <v>8000</v>
@@ -7376,7 +7376,7 @@
         <v>102</v>
       </c>
       <c r="AA75">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB75">
         <v>8000</v>
@@ -7465,7 +7465,7 @@
         <v>101</v>
       </c>
       <c r="AA76">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB76">
         <v>8000</v>
@@ -7910,7 +7910,7 @@
         <v>101</v>
       </c>
       <c r="AA81">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB81">
         <v>8000</v>
@@ -7999,7 +7999,7 @@
         <v>101</v>
       </c>
       <c r="AA82">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB82">
         <v>8000</v>
@@ -8088,7 +8088,7 @@
         <v>101</v>
       </c>
       <c r="AA83">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB83">
         <v>8000</v>
@@ -8177,7 +8177,7 @@
         <v>101</v>
       </c>
       <c r="AA84">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB84">
         <v>8000</v>
@@ -8266,7 +8266,7 @@
         <v>101</v>
       </c>
       <c r="AA85">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB85">
         <v>8000</v>
@@ -8355,7 +8355,7 @@
         <v>101</v>
       </c>
       <c r="AA86">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB86">
         <v>8000</v>
@@ -8444,7 +8444,7 @@
         <v>101</v>
       </c>
       <c r="AA87">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB87">
         <v>8000</v>
@@ -8533,7 +8533,7 @@
         <v>101</v>
       </c>
       <c r="AA88">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB88">
         <v>8000</v>
@@ -8622,7 +8622,7 @@
         <v>101</v>
       </c>
       <c r="AA89">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB89">
         <v>8000</v>
@@ -8711,7 +8711,7 @@
         <v>101</v>
       </c>
       <c r="AA90">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB90">
         <v>8000</v>
@@ -8800,7 +8800,7 @@
         <v>101</v>
       </c>
       <c r="AA91">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB91">
         <v>8000</v>
@@ -8889,7 +8889,7 @@
         <v>102</v>
       </c>
       <c r="AA92">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB92">
         <v>8000</v>
@@ -8978,7 +8978,7 @@
         <v>102</v>
       </c>
       <c r="AA93">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB93">
         <v>8000</v>
@@ -9067,7 +9067,7 @@
         <v>102</v>
       </c>
       <c r="AA94">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB94">
         <v>8000</v>
@@ -9156,7 +9156,7 @@
         <v>102</v>
       </c>
       <c r="AA95">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB95">
         <v>8000</v>
@@ -9245,7 +9245,7 @@
         <v>102</v>
       </c>
       <c r="AA96">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB96">
         <v>8000</v>
@@ -9334,7 +9334,7 @@
         <v>102</v>
       </c>
       <c r="AA97">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB97">
         <v>8000</v>
@@ -9423,7 +9423,7 @@
         <v>102</v>
       </c>
       <c r="AA98">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB98">
         <v>8000</v>
@@ -9512,7 +9512,7 @@
         <v>101</v>
       </c>
       <c r="AA99">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB99">
         <v>8000</v>
@@ -9601,7 +9601,7 @@
         <v>101</v>
       </c>
       <c r="AA100">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB100">
         <v>8000</v>
@@ -9690,7 +9690,7 @@
         <v>101</v>
       </c>
       <c r="AA101">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB101">
         <v>8000</v>
@@ -9779,7 +9779,7 @@
         <v>101</v>
       </c>
       <c r="AA102">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB102">
         <v>8000</v>
@@ -9868,7 +9868,7 @@
         <v>101</v>
       </c>
       <c r="AA103">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB103">
         <v>8000</v>
@@ -9957,7 +9957,7 @@
         <v>101</v>
       </c>
       <c r="AA104">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB104">
         <v>8000</v>
@@ -10046,7 +10046,7 @@
         <v>101</v>
       </c>
       <c r="AA105">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB105">
         <v>8000</v>
@@ -10135,7 +10135,7 @@
         <v>101</v>
       </c>
       <c r="AA106">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB106">
         <v>8000</v>
@@ -10224,7 +10224,7 @@
         <v>101</v>
       </c>
       <c r="AA107">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB107">
         <v>8000</v>
@@ -10313,7 +10313,7 @@
         <v>101</v>
       </c>
       <c r="AA108">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AB108">
         <v>8000</v>
